--- a/artfynd/A 37358-2025 artfynd.xlsx
+++ b/artfynd/A 37358-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,6 +1012,121 @@
           <t>Billingens flora</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130746898</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1879</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trollsmultron</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Drymocallis rupestris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soják</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skövde - Lerdalavägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>428104</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6476151</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Parkeringsplats - Blängsmossen</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37358-2025 artfynd.xlsx
+++ b/artfynd/A 37358-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>130746898</v>
       </c>
       <c r="B5" t="n">
-        <v>102559</v>
+        <v>102572</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37358-2025 artfynd.xlsx
+++ b/artfynd/A 37358-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>130746898</v>
       </c>
       <c r="B5" t="n">
-        <v>102572</v>
+        <v>102573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37358-2025 artfynd.xlsx
+++ b/artfynd/A 37358-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>130746898</v>
       </c>
       <c r="B5" t="n">
-        <v>102573</v>
+        <v>102576</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37358-2025 artfynd.xlsx
+++ b/artfynd/A 37358-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>130746898</v>
       </c>
       <c r="B5" t="n">
-        <v>102576</v>
+        <v>102590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37358-2025 artfynd.xlsx
+++ b/artfynd/A 37358-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>130746898</v>
       </c>
       <c r="B5" t="n">
-        <v>102590</v>
+        <v>102608</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37358-2025 artfynd.xlsx
+++ b/artfynd/A 37358-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>130746898</v>
       </c>
       <c r="B5" t="n">
-        <v>102608</v>
+        <v>102622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37358-2025 artfynd.xlsx
+++ b/artfynd/A 37358-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64361940</v>
+        <v>130746898</v>
       </c>
       <c r="B2" t="n">
-        <v>98021</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>1879</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Trollsmultron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Drymocallis rupestris</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Soják</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -715,16 +714,18 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsaborg norr om, Vg</t>
+          <t>Skövde - Lerdalavägen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>427947</v>
+        <v>428104</v>
       </c>
       <c r="R2" t="n">
-        <v>6476293</v>
+        <v>6476151</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,17 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-06-23</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-06-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Väg 2752 - Vägdiken sträckan Åsaborg NO om</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,37 +766,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Parkeringsplats - Blängsmossen</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87985796</v>
+        <v>122997880</v>
       </c>
       <c r="B3" t="n">
-        <v>103528</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +801,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsaborg, Vg</t>
+          <t>Blängs mosse , Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427921</v>
+        <v>428044</v>
       </c>
       <c r="R3" t="n">
-        <v>6476171</v>
+        <v>6476195</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,12 +864,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-07-25</t>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-07-25</t>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,40 +890,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Landsväg, skogsvägar, skog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Annelie Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+          <t>Annelie Andersson, Kjell Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88019956</v>
+        <v>122997887</v>
       </c>
       <c r="B4" t="n">
-        <v>100188</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,37 +917,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Katrinelund, Vg</t>
+          <t>Blängs mosse , Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428092</v>
+        <v>428044</v>
       </c>
       <c r="R4" t="n">
-        <v>6476152</v>
+        <v>6476195</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,12 +980,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,38 +1004,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Vägkant, barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Annelie Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+          <t>Annelie Andersson, Kjell Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130746898</v>
+        <v>110304503</v>
       </c>
       <c r="B5" t="n">
-        <v>102640</v>
+        <v>43378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,49 +1033,54 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1879</v>
+        <v>201075</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trollsmultron</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Drymocallis rupestris</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soják</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skövde - Lerdalavägen, Vg</t>
+          <t>Blängsmossens parkering, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428104</v>
+        <v>428070</v>
       </c>
       <c r="R5" t="n">
-        <v>6476151</v>
+        <v>6476157</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,12 +1104,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,23 +1132,1448 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Parkeringsplats - Blängsmossen</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Per-Olof Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per-Olof Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110304408</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43309</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Blängsmossens parkering, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>428070</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6476157</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per-Olof Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per-Olof Bengtsson, Annelie Andersson, Kjell Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110304402</v>
+      </c>
+      <c r="B7" t="n">
+        <v>45042</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>201164</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Zygaena filipendulae</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blängsmossens parkering, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>428070</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6476157</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per-Olof Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per-Olof Bengtsson, Annelie Andersson, Kjell Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>87985812</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Åsaborg, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>427952</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6476289</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2007-07-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2007-07-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Landsväg, skogsvägar, skog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Kurt-Anders Johansson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>88019925</v>
+      </c>
+      <c r="B9" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Katrinelund, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>428281</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6476107</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2010-06-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2010-06-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Vägkant, barrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>88019978</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Katrinelund, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>428216</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6476139</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Vägkant, barrskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118618741</v>
+      </c>
+      <c r="B11" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Åsaborg Norr, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>427978</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6476165</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Skogsväg</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>87985788</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Åsaborg, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>427901</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6476153</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2007-07-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2007-07-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Landsväg, skogsvägar, skog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>87985796</v>
+      </c>
+      <c r="B13" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Åsaborg, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>427921</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6476171</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2007-07-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2007-07-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Landsväg, skogsvägar, skog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>88019956</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Katrinelund, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>428092</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6476152</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Vägkant, barrskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>64361939</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Åsaborg norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>427987</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6476242</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2010-06-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2010-06-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Väg 2752 - Vägdiken sträckan Åsaborg NO om</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>87985814</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Åsaborg, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>428012</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6476221</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2007-07-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2007-07-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Landsväg, skogsvägar, skog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>64361940</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Åsaborg norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>427947</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6476293</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2010-06-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2010-06-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Väg 2752 - Vägdiken sträckan Åsaborg NO om</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>88019979</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Katrinelund, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>428216</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6476139</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Vägkant, barrskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37358-2025 artfynd.xlsx
+++ b/artfynd/A 37358-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130746898</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122997880</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122997887</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110304503</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1269,6 +1294,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110304408</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1394,6 +1424,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110304402</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87985812</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1606,6 +1646,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88019925</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1712,6 +1757,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88019978</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1818,6 +1868,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118618741</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1924,6 +1979,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87985788</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2030,6 +2090,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87985796</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2137,6 +2202,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88019956</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2253,6 +2323,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64361939</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2359,6 +2434,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87985814</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2471,6 +2551,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64361940</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2574,8 +2659,32 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88019979</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>